--- a/data/dividends_info_20260701.xlsx
+++ b/data/dividends_info_20260701.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>65.48999786376953</v>
+        <v>62.36999893188477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1374255656370847</v>
+        <v>0.1443001467713514</v>
       </c>
       <c r="J2" t="n">
         <v>257</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.34999847412109</v>
+        <v>65.69999694824219</v>
       </c>
       <c r="I3" t="n">
-        <v>1.071155342531803</v>
+        <v>1.065449060144482</v>
       </c>
       <c r="J3" t="n">
         <v>236</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.159999847412109</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6550218449725329</v>
+        <v>0.6437768451142812</v>
       </c>
       <c r="J4" t="n">
         <v>166</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>65.48999786376953</v>
+        <v>62.36999893188477</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1374255656370847</v>
+        <v>0.1443001467713514</v>
       </c>
       <c r="J6" t="n">
         <v>166</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.029999971389771</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="I7" t="n">
-        <v>3.79310350173476</v>
+        <v>3.719806883248261</v>
       </c>
       <c r="J7" t="n">
         <v>145</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20.32999992370605</v>
+        <v>20.07999992370605</v>
       </c>
       <c r="I8" t="n">
-        <v>1.328086576553122</v>
+        <v>1.344621519053112</v>
       </c>
       <c r="J8" t="n">
         <v>145</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.829999923706055</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I9" t="n">
-        <v>3.430531777311974</v>
+        <v>3.436426015480821</v>
       </c>
       <c r="J9" t="n">
         <v>138</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.75</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7643312194767268</v>
       </c>
       <c r="J10" t="n">
         <v>110</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20.32999992370605</v>
+        <v>20.07999992370605</v>
       </c>
       <c r="I14" t="n">
-        <v>1.328086576553122</v>
+        <v>1.344621519053112</v>
       </c>
       <c r="J14" t="n">
         <v>82</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65.48999786376953</v>
+        <v>62.36999893188477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1374255656370847</v>
+        <v>0.1443001467713514</v>
       </c>
       <c r="J15" t="n">
         <v>82</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.619999885559082</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="I19" t="n">
-        <v>4.448398667095876</v>
+        <v>4.409171016509162</v>
       </c>
       <c r="J19" t="n">
         <v>26</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.199999809265137</v>
+        <v>4.150000095367432</v>
       </c>
       <c r="I20" t="n">
-        <v>3.333333484710216</v>
+        <v>3.373493898380374</v>
       </c>
       <c r="J20" t="n">
         <v>19</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.02400016784668</v>
+        <v>9.961999893188477</v>
       </c>
       <c r="I21" t="n">
-        <v>2.59377489671224</v>
+        <v>2.609917715194669</v>
       </c>
       <c r="J21" t="n">
         <v>19</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.80000019073486</v>
+        <v>14.85999965667725</v>
       </c>
       <c r="I22" t="n">
-        <v>4.05405400180747</v>
+        <v>4.037685153851224</v>
       </c>
       <c r="J22" t="n">
         <v>19</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.766000032424927</v>
+        <v>2.812000036239624</v>
       </c>
       <c r="I23" t="n">
-        <v>7.953723695625847</v>
+        <v>7.823612985944242</v>
       </c>
       <c r="J23" t="n">
         <v>19</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.670000076293945</v>
+        <v>6.659999847412109</v>
       </c>
       <c r="I25" t="n">
-        <v>3.598200858392663</v>
+        <v>3.603603686166109</v>
       </c>
       <c r="J25" t="n">
         <v>19</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19.29999923706055</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="I26" t="n">
-        <v>1.948186605510281</v>
+        <v>1.918367309602089</v>
       </c>
       <c r="J26" t="n">
         <v>19</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3.059999942779541</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="I29" t="n">
-        <v>4.901960875977926</v>
+        <v>4.934210588231972</v>
       </c>
       <c r="J29" t="n">
         <v>12</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.279999971389771</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I30" t="n">
-        <v>3.728070222219713</v>
+        <v>3.828828779484834</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.739999771118164</v>
+        <v>4.840000152587891</v>
       </c>
       <c r="I31" t="n">
-        <v>1.476793320255521</v>
+        <v>1.446280946139471</v>
       </c>
       <c r="J31" t="n">
         <v>5</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>33.54999923706055</v>
+        <v>37.20000076293945</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4470938998839218</v>
+        <v>0.4032257981818045</v>
       </c>
       <c r="J32" t="n">
         <v>5</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.36000061035156</v>
+        <v>21.44000053405762</v>
       </c>
       <c r="I34" t="n">
-        <v>1.170411951574777</v>
+        <v>1.166044747073923</v>
       </c>
       <c r="J34" t="n">
         <v>-9</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>31.79999923706055</v>
+        <v>32.09999847412109</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6132075618817686</v>
+        <v>0.6074766643905243</v>
       </c>
       <c r="J35" t="n">
         <v>-9</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.879999995231628</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="I36" t="n">
-        <v>1.755319153388305</v>
+        <v>1.736842127057654</v>
       </c>
       <c r="J36" t="n">
         <v>-9</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.139999866485596</v>
+        <v>5.175000190734863</v>
       </c>
       <c r="I37" t="n">
-        <v>5.642023492858249</v>
+        <v>5.603864527758002</v>
       </c>
       <c r="J37" t="n">
         <v>-9</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.608000040054321</v>
+        <v>3.651999950408936</v>
       </c>
       <c r="I38" t="n">
-        <v>4.434589751212727</v>
+        <v>4.381161067159486</v>
       </c>
       <c r="J38" t="n">
         <v>-9</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.430000066757202</v>
+        <v>2.447999954223633</v>
       </c>
       <c r="I39" t="n">
-        <v>5.703703547010992</v>
+        <v>5.661764811754503</v>
       </c>
       <c r="J39" t="n">
         <v>-9</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>48.70500183105469</v>
+        <v>48.7599983215332</v>
       </c>
       <c r="I40" t="n">
-        <v>1.293501645242331</v>
+        <v>1.292042702392346</v>
       </c>
       <c r="J40" t="n">
         <v>-9</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5.940000057220459</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="I41" t="n">
-        <v>2.356902334198143</v>
+        <v>2.310231044916251</v>
       </c>
       <c r="J41" t="n">
         <v>-9</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>16.60000038146973</v>
+        <v>16.70000076293945</v>
       </c>
       <c r="I42" t="n">
-        <v>4.698795072744092</v>
+        <v>4.670658469255712</v>
       </c>
       <c r="J42" t="n">
         <v>-9</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.70999908447266</v>
+        <v>29.01000022888184</v>
       </c>
       <c r="I43" t="n">
-        <v>2.960640986086652</v>
+        <v>2.930024106493302</v>
       </c>
       <c r="J43" t="n">
         <v>-9</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>65.48999786376953</v>
+        <v>62.36999893188477</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1374255656370847</v>
+        <v>0.1443001467713514</v>
       </c>
       <c r="J44" t="n">
         <v>-9</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.379999995231628</v>
+        <v>1.360000014305115</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7246376836632911</v>
+        <v>0.7352941099128922</v>
       </c>
       <c r="J45" t="n">
         <v>-9</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.190000057220459</v>
+        <v>6.185999870300293</v>
       </c>
       <c r="I46" t="n">
-        <v>2.928917581971889</v>
+        <v>2.930811571310282</v>
       </c>
       <c r="J46" t="n">
         <v>-9</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.100000381469727</v>
+        <v>9.510000228881836</v>
       </c>
       <c r="I47" t="n">
-        <v>2.857142737372147</v>
+        <v>2.733964182360174</v>
       </c>
       <c r="J47" t="n">
         <v>-9</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.10000038146973</v>
+        <v>10.09500026702881</v>
       </c>
       <c r="I48" t="n">
-        <v>2.742574153840692</v>
+        <v>2.743932567339372</v>
       </c>
       <c r="J48" t="n">
         <v>-9</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9720000028610229</v>
+        <v>0.9779999852180481</v>
       </c>
       <c r="I49" t="n">
-        <v>1.388888884800779</v>
+        <v>1.380368119023042</v>
       </c>
       <c r="J49" t="n">
         <v>-16</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.026000022888184</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="I50" t="n">
-        <v>3.635161902444728</v>
+        <v>3.63036307058268</v>
       </c>
       <c r="J50" t="n">
         <v>-16</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.690000057220459</v>
+        <v>1.649999976158142</v>
       </c>
       <c r="I51" t="n">
-        <v>1.420118295112532</v>
+        <v>1.454545475563071</v>
       </c>
       <c r="J51" t="n">
         <v>-16</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.890000104904175</v>
+        <v>2.934999942779541</v>
       </c>
       <c r="I52" t="n">
-        <v>5.536331978967358</v>
+        <v>5.451448147166734</v>
       </c>
       <c r="J52" t="n">
         <v>-23</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.20000076293945</v>
+        <v>27.14999961853027</v>
       </c>
       <c r="I54" t="n">
-        <v>4.080882238475512</v>
+        <v>4.088397847499079</v>
       </c>
       <c r="J54" t="n">
         <v>-27</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8690000176429749</v>
+        <v>0.8659999966621399</v>
       </c>
       <c r="I55" t="n">
-        <v>3.452243888483484</v>
+        <v>3.464203246608575</v>
       </c>
       <c r="J55" t="n">
         <v>-30</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4639999866485596</v>
+        <v>0.4580000042915344</v>
       </c>
       <c r="I56" t="n">
-        <v>4.956896694357135</v>
+        <v>5.02183401407997</v>
       </c>
       <c r="J56" t="n">
         <v>-30</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.380000114440918</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="I58" t="n">
-        <v>2.132196136032998</v>
+        <v>2.217294787694346</v>
       </c>
       <c r="J58" t="n">
         <v>-30</v>
@@ -3178,7 +3178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C132"/>
+  <dimension ref="A1:C172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3320,7 +3320,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3330,14 +3330,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3347,14 +3347,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3364,14 +3364,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3381,14 +3381,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3456,7 +3456,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3490,7 +3490,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3500,14 +3500,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3517,14 +3517,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3602,14 +3602,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3619,14 +3619,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3636,14 +3636,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3670,14 +3670,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3687,14 +3687,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3755,14 +3755,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3772,14 +3772,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3789,14 +3789,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3881,126 +3881,126 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4010,14 +4010,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4044,14 +4044,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4078,36 +4078,36 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4119,12 +4119,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4136,63 +4136,63 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4221,29 +4221,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4255,7 +4255,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4265,14 +4265,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4282,14 +4282,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4306,7 +4306,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4323,7 +4323,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4357,7 +4357,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4374,7 +4374,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4401,14 +4401,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4425,7 +4425,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4435,14 +4435,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4459,7 +4459,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4476,7 +4476,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4486,14 +4486,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4503,14 +4503,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4520,14 +4520,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4537,14 +4537,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4554,14 +4554,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4588,14 +4588,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4612,7 +4612,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4622,14 +4622,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4639,53 +4639,53 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4697,29 +4697,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4731,29 +4731,29 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4765,58 +4765,58 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4826,14 +4826,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4843,14 +4843,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4860,14 +4860,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4877,14 +4877,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4894,14 +4894,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4911,14 +4911,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4928,14 +4928,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4945,14 +4945,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4969,7 +4969,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4979,14 +4979,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5003,7 +5003,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5037,7 +5037,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>CASTELLO SGR S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5064,14 +5064,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5088,7 +5088,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5105,7 +5105,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5115,14 +5115,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5139,7 +5139,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5149,14 +5149,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5207,7 +5207,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5224,7 +5224,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5251,14 +5251,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5275,7 +5275,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5285,121 +5285,121 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5411,17 +5411,697 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>Banca Profilo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>First Capital S.p.A.</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Half Year Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Gabetti Property Solutions S.p.A.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>IREN S.p.A.</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Industrie De Nora S.p.A.</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Industrie De Nora S.p.A.</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Alerion Clean Power S.p.A.</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AZIMUT HOLDING S.p.A.</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ASCOPIAVE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ASCOPIAVE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AMPLIFON S.p.A.</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>AMPLIFON S.p.A.</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AEDES S.p.A.</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>A2A S.p.A.</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TECHNOGYM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ESAUTOMOTION S.p.A.</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Half Year Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ENEL S.p.A.</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Svas Biosana S.p.A.</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Half Year Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>DiaSorin S.p.A</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Tinexta S.p.A.</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Tinexta S.p.A.</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Ferretti S.p.A.</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ERG S.p.A.</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>BIESSE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Nusco S.p.A.</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Half Year Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Basic Net S.p.A.</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Half Year Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
           <t>Comer Industries S.p.A.</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>VNE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ERG S.p.A.</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Basic Net S.p.A.</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>GREEN OLEO S.p.A</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -5449,7 +6129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5472,7 +6152,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5489,24 +6169,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5516,14 +6196,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5540,7 +6220,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5550,14 +6230,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5567,31 +6247,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5608,7 +6288,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5618,41 +6298,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
